--- a/MatrixProfile/results/results_final_final_evaluation/hp_tuning_mp_results_resp_detection_window_relative.xlsx
+++ b/MatrixProfile/results/results_final_final_evaluation/hp_tuning_mp_results_resp_detection_window_relative.xlsx
@@ -570,7 +570,7 @@
         <v>739</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O2" t="n">
         <v>0.3803680981595092</v>
@@ -579,10 +579,10 @@
         <v>1.900611316950579</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.908911099750946</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>739</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O3" t="n">
         <v>0.9815950920245399</v>
@@ -644,10 +644,10 @@
         <v>13.89541569459927</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>13.27458957450171</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>739</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
         <v>0.9693251533742331</v>
@@ -709,10 +709,10 @@
         <v>11.36695365382482</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>10.91840759605786</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
